--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/nuble.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/nuble.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>15156.18</v>
+        <v>15074.98</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>16049.59</v>
+        <v>16286.38</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>73466.35000000001</v>
+        <v>73056.42999999999</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>9213.620000000001</v>
+        <v>9008.85</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>8530.68</v>
+        <v>8451.76</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/nuble.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/nuble.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1233616-170-CM26</t>
+          <t>2705-1005-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,27 +524,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>61.980.940-8</t>
+          <t>60.911.006-6</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Punilla Cordil</t>
+          <t>UNIVERSIDAD DEL BIO BIO</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>CLARO CHILE S.A.</t>
+          <t>TCHILECOM</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>96.799.250-k</t>
+          <t>77.349.120-8</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>15074.98</v>
+        <v>6629.46</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1057506-2288-CM25</t>
+          <t>1233616-170-CM26</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>61.602.194-K</t>
+          <t>61.980.940-8</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COELEMU</t>
+          <t>Servicio Local de Educación Pública Punilla Cordil</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>GEORG</t>
+          <t>CLARO CHILE S.A.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>76.624.276-6</t>
+          <t>96.799.250-k</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>16286.38</v>
+        <v>15074.98</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1040758-18-CM26</t>
+          <t>1057506-2288-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61.601.000-k</t>
+          <t>61.602.194-K</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COELEMU</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
+          <t>GEORG</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>76.304.354-1</t>
+          <t>76.624.276-6</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>73056.42999999999</v>
+        <v>16286.38</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1036569-50-CM26</t>
+          <t>1040758-18-CM26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>62.000.390-5</t>
+          <t>61.601.000-k</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gobierno Regional de Ñuble</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>VICTORIA SPA</t>
+          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>76.188.587-1</t>
+          <t>76.304.354-1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>9008.85</v>
+        <v>73056.42999999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1036569-66-CM26</t>
+          <t>1036569-50-CM26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,17 +768,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>COMPUNET S.P.A.</t>
+          <t>VICTORIA SPA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>78.466.220-9</t>
+          <t>76.188.587-1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,6 +813,67 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
+        <v>9008.85</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1036569-66-CM26</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>62.000.390-5</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Gobierno Regional de Ñuble</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>COMPUNET S.P.A.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>78.466.220-9</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="n">
         <v>8451.76</v>
       </c>
     </row>

--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/nuble.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/nuble.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ñuble" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Ñuble" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2705-1005-CM25</t>
+          <t>1233616-16-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,27 +524,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ago-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-01-29</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>60.911.006-6</t>
+          <t>61.980.940-8</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DEL BIO BIO</t>
+          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>TCHILECOM</t>
+          <t>CLARO CHILE S.A.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>77.349.120-8</t>
+          <t>96.799.250-k</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>6629.46</v>
+        <v>13532.73</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1233616-170-CM26</t>
+          <t>1040758-2-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2025-02-12</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>61.980.940-8</t>
+          <t>61.601.000-k</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Punilla Cordil</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CLARO CHILE S.A.</t>
+          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>96.799.250-k</t>
+          <t>76.304.354-1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>15074.98</v>
+        <v>23896.97</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1057506-2288-CM25</t>
+          <t>1155683-408-CM24</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61.602.194-K</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COELEMU</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>GEORG</t>
+          <t>VICTORIA SpA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>76.624.276-6</t>
+          <t>76.188.587-1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>16286.38</v>
+        <v>8288.549999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1040758-18-CM26</t>
+          <t>2705-1005-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,27 +707,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>61.601.000-k</t>
+          <t>60.911.006-6</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>UNIVERSIDAD DEL BIO BIO</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
+          <t>TCHILECOM</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>76.304.354-1</t>
+          <t>77.349.120-8</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>73056.42999999999</v>
+        <v>6629.46</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1036569-50-CM26</t>
+          <t>1036569-156-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,17 +768,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Gobierno Regional de Ñuble</t>
+          <t>GOBIERNO REGIONAL DE ÑUBLE</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>VICTORIA SPA</t>
+          <t>COMPUNET S.P.A.</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>76.188.587-1</t>
+          <t>78.466.220-9</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>9008.85</v>
+        <v>6637.12</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1036569-66-CM26</t>
+          <t>1233616-170-CM26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,27 +829,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>62.000.390-5</t>
+          <t>61.980.940-8</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gobierno Regional de Ñuble</t>
+          <t>Servicio Local de Educación Pública Punilla Cordil</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>COMPUNET S.P.A.</t>
+          <t>CLARO CHILE S.A.</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>78.466.220-9</t>
+          <t>96.799.250-k</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,6 +874,250 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
+        <v>15074.98</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1057506-2288-CM25</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>61.602.194-K</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COELEMU</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>GEORG</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>76.624.276-6</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>16286.38</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1040758-18-CM26</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>61.601.000-k</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>76.304.354-1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>73056.42999999999</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>1036569-50-CM26</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>62.000.390-5</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Gobierno Regional de Ñuble</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>VICTORIA SPA</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>76.188.587-1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>9008.85</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>1036569-66-CM26</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>62.000.390-5</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Gobierno Regional de Ñuble</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>COMPUNET S.P.A.</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>78.466.220-9</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="n">
         <v>8451.76</v>
       </c>
     </row>

--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/nuble.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/nuble.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -849,7 +849,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Punilla Cordil</t>
+          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>GEORG</t>
+          <t>Georg</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Gobierno Regional de Ñuble</t>
+          <t>GOBIERNO REGIONAL DE ÑUBLE</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>VICTORIA SPA</t>
+          <t>VICTORIA SpA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Gobierno Regional de Ñuble</t>
+          <t>GOBIERNO REGIONAL DE ÑUBLE</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1119,6 +1119,128 @@
       </c>
       <c r="M11" s="2" t="n">
         <v>8451.76</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>1016-89-CM26</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>SAARGO SPA</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>76.891.821-k</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>15439.79</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>1016-90-CM26</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>USERCODE SPA</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>77.347.464-8</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>36548.13</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/nuble.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/nuble.xlsx
@@ -562,7 +562,11 @@
           <t>96.799.250-k</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>76.304.354-1</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>76.188.587-1</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +879,11 @@
           <t>96.799.250-k</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +944,11 @@
           <t>76.624.276-6</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1009,11 @@
           <t>76.304.354-1</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1074,11 @@
           <t>76.188.587-1</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1200,11 @@
           <t>76.891.821-k</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1265,11 @@
           <t>77.347.464-8</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
